--- a/生物化学实验(Biochemistry Lab)/开放实验/开放实验酶标仪数据/磷硫铁法/3组磷硫铁法预实验-3.xlsx
+++ b/生物化学实验(Biochemistry Lab)/开放实验/开放实验酶标仪数据/磷硫铁法/3组磷硫铁法预实验-3.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11211"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/peiyuliu/Desktop/PKU-Undergraduate-Course-Public/生物化学实验(Biochemistry Lab)/开放实验/开放实验酶标仪数据/磷硫铁法/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E271CC4D-E4C2-7242-A602-7BD323F4335E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="120" windowWidth="9435" windowHeight="6915"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="板 1 - Sheet1" sheetId="1" r:id="rId1"/>
@@ -13,8 +19,42 @@
     <definedName name="MethodPointer1">-704612208</definedName>
     <definedName name="MethodPointer2">344</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -325,7 +365,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6">
     <font>
       <sz val="10"/>
@@ -536,34 +576,551 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="zh-CN"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>反应10分钟</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'板 1 - Sheet1'!$T$27:$T$39</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>0.13999999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.0000000000000016E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.0000000000000008E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.0000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.0000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8.0000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2E-3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'板 1 - Sheet1'!$V$27:$V$39</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>2.339</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.9460000000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.5640000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.2370000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.78749999999999998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.69650000000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.27749999999999997</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.16299999999999998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.10349999999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6.7999999999999991E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>6.0000000000000053E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-68F1-8A4B-8B15-D7DBCC1A3F0C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>反应20分钟</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'板 1 - Sheet1'!$T$27:$T$39</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>0.13999999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.0000000000000016E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.0000000000000008E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.0000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.0000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8.0000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2E-3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'板 1 - Sheet1'!$W$27:$W$39</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>2.3479999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.0249999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.637</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.3499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.88500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.749</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.315</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.18049999999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.11600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7.2499999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>6.5000000000000058E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-F5F3-2748-8D61-A5A3B3C68C62}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="143281536"/>
+        <c:axId val="143303808"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="143281536"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:tint val="75000"/>
+                <a:shade val="95000"/>
+                <a:satMod val="105000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="143303808"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="143303808"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:tint val="75000"/>
+                <a:shade val="95000"/>
+                <a:satMod val="105000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="143281536"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000011" l="0.70000000000000007" r="0.70000000000000007" t="0.75000000000000011" header="0.30000000000000004" footer="0.30000000000000004"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:v>反应10分钟</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
           <c:trendline>
-            <c:trendlineType val="linear"/>
-          </c:trendline>
-          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:trendlineType val="linear"/>
             <c:dispRSqr val="1"/>
             <c:dispEq val="1"/>
             <c:trendlineLbl>
-              <c:layout/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-2.9251749781277342E-2"/>
+                  <c:y val="0.26911927675707203"/>
+                </c:manualLayout>
+              </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-CN"/>
+                </a:p>
+              </c:txPr>
             </c:trendlineLbl>
           </c:trendline>
           <c:xVal>
@@ -573,40 +1130,40 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>1.4</c:v>
+                  <c:v>0.13999999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.2</c:v>
+                  <c:v>0.12</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.8</c:v>
+                  <c:v>8.0000000000000016E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.6</c:v>
+                  <c:v>0.06</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.4</c:v>
+                  <c:v>4.0000000000000008E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.2</c:v>
+                  <c:v>2.0000000000000004E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1</c:v>
+                  <c:v>1.0000000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.08</c:v>
+                  <c:v>8.0000000000000002E-3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.04</c:v>
+                  <c:v>4.0000000000000001E-3</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.02</c:v>
+                  <c:v>2E-3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.01</c:v>
+                  <c:v>1E-3</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0</c:v>
@@ -616,95 +1173,1463 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'板 1 - Sheet1'!$U$27:$U$39</c:f>
+              <c:f>'板 1 - Sheet1'!$V$27:$V$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>2.415</c:v>
+                  <c:v>2.339</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.0220000000000002</c:v>
+                  <c:v>1.9460000000000002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.6400000000000001</c:v>
+                  <c:v>1.5640000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.3130000000000002</c:v>
+                  <c:v>1.2370000000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.86349999999999993</c:v>
+                  <c:v>0.78749999999999998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.77249999999999996</c:v>
+                  <c:v>0.69650000000000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.35349999999999998</c:v>
+                  <c:v>0.27749999999999997</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.23899999999999999</c:v>
+                  <c:v>0.16299999999999998</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.17949999999999999</c:v>
+                  <c:v>0.10349999999999999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.14399999999999999</c:v>
+                  <c:v>6.7999999999999991E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.12</c:v>
+                  <c:v>4.3999999999999997E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>8.2000000000000003E-2</c:v>
+                  <c:v>6.0000000000000053E-3</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>7.6000000000000012E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-55E3-4A4C-8C3F-48E78441340F}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
-        <c:axId val="143281536"/>
-        <c:axId val="143303808"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>反应20分钟</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.14869619422572178"/>
+                  <c:y val="6.0075823855351414E-4"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="accent3"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-CN"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'板 1 - Sheet1'!$T$27:$T$39</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>0.13999999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.0000000000000016E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.0000000000000008E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.0000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.0000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8.0000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2E-3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'板 1 - Sheet1'!$W$27:$W$39</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>2.3479999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.0249999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.637</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.3499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.88500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.749</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.315</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.18049999999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.11600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7.2499999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>6.5000000000000058E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-55E3-4A4C-8C3F-48E78441340F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1695308016"/>
+        <c:axId val="1695461712"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="143281536"/>
+        <c:axId val="1695308016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="143303808"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1695461712"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="143303808"/>
+        <c:axId val="1695461712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="143281536"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1695308016"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="r"/>
-      <c:layout/>
+      <c:legendPos val="t"/>
+      <c:legendEntry>
+        <c:idx val="2"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="3"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-CN"/>
+        </a:p>
+      </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-CN"/>
+    </a:p>
+  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000011" l="0.70000000000000007" r="0.70000000000000007" t="0.75000000000000011" header="0.30000000000000004" footer="0.30000000000000004"/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="11">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent5"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="11">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent5"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="102">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1">
+        <a:tint val="75000"/>
+      </a:schemeClr>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1">
+        <a:tint val="75000"/>
+      </a:schemeClr>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <a:schemeClr val="bg1"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:lineWidthScale>3</cs:lineWidthScale>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln cap="rnd">
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1">
+        <a:tint val="75000"/>
+      </a:schemeClr>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <a:schemeClr val="dk1">
+        <a:tint val="95000"/>
+      </a:schemeClr>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <a:schemeClr val="tx1"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1">
+        <a:tint val="75000"/>
+      </a:schemeClr>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1">
+        <a:tint val="75000"/>
+      </a:schemeClr>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1">
+        <a:tint val="50000"/>
+      </a:schemeClr>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <a:schemeClr val="bg1"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1">
+        <a:tint val="75000"/>
+      </a:schemeClr>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln cap="rnd">
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <a:schemeClr val="dk1">
+        <a:tint val="5000"/>
+      </a:schemeClr>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="1">
+      <a:schemeClr val="tx1">
+        <a:tint val="75000"/>
+      </a:schemeClr>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -712,19 +2637,25 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:colOff>349250</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:colOff>654050</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="图表 1"/>
+        <xdr:cNvPr id="2" name="图表 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -739,11 +2670,47 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>169708</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>67434</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>21354</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>135767</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90B8E5A8-3B02-3140-9256-7EE3001892E4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -785,7 +2752,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -817,9 +2784,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -851,6 +2836,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1026,15 +3029,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:U39"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A2:AB51"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" ht="14">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1042,7 +3045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" ht="14">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -1050,12 +3053,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:21" ht="14">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:21" ht="14">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -1063,7 +3066,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:21" ht="14">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -1071,7 +3074,7 @@
         <v>45618</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:21" ht="14">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -1079,7 +3082,7 @@
         <v>0.71670138888888879</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:21" ht="14">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -1087,7 +3090,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:21" ht="14">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -1095,7 +3098,7 @@
         <v>19012425</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:21" ht="14">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -1103,13 +3106,13 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:21">
+    <row r="13" spans="1:21" ht="14">
       <c r="A13" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="5"/>
     </row>
-    <row r="14" spans="1:21">
+    <row r="14" spans="1:21" ht="14">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -1117,12 +3120,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:21">
+    <row r="15" spans="1:21" ht="14">
       <c r="A15" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:21">
+    <row r="16" spans="1:21" ht="14">
       <c r="A16" s="1" t="s">
         <v>18</v>
       </c>
@@ -1143,7 +3146,7 @@
         <v>3.2250000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:21">
+    <row r="17" spans="1:26" ht="14">
       <c r="B17" s="1" t="s">
         <v>20</v>
       </c>
@@ -1154,7 +3157,7 @@
         <v>3.141</v>
       </c>
     </row>
-    <row r="18" spans="1:21">
+    <row r="18" spans="1:26" ht="14">
       <c r="B18" s="1" t="s">
         <v>21</v>
       </c>
@@ -1172,7 +3175,7 @@
         <v>3.2810000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:21">
+    <row r="19" spans="1:26" ht="14">
       <c r="B19" s="1" t="s">
         <v>22</v>
       </c>
@@ -1190,7 +3193,7 @@
         <v>3.3520000000000003</v>
       </c>
     </row>
-    <row r="20" spans="1:21">
+    <row r="20" spans="1:26">
       <c r="R20" s="15">
         <v>2.9460000000000002</v>
       </c>
@@ -1205,7 +3208,7 @@
         <v>3.13</v>
       </c>
     </row>
-    <row r="21" spans="1:21">
+    <row r="21" spans="1:26" ht="14">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -1224,7 +3227,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="22" spans="1:21">
+    <row r="22" spans="1:26" ht="14">
       <c r="A22" s="1" t="s">
         <v>24</v>
       </c>
@@ -1245,7 +3248,7 @@
         <v>2.786</v>
       </c>
     </row>
-    <row r="23" spans="1:21">
+    <row r="23" spans="1:26">
       <c r="R23" s="15">
         <v>3.0880000000000001</v>
       </c>
@@ -1253,7 +3256,7 @@
         <v>2.1219999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:21">
+    <row r="24" spans="1:26">
       <c r="B24" s="6"/>
       <c r="C24" s="7">
         <v>1</v>
@@ -1298,7 +3301,7 @@
         <v>2.1309999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:21">
+    <row r="25" spans="1:26" ht="14">
       <c r="B25" s="7" t="s">
         <v>25</v>
       </c>
@@ -1355,7 +3358,7 @@
         <v>2.7919999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:21">
+    <row r="26" spans="1:26" ht="14">
       <c r="B26" s="7" t="s">
         <v>26</v>
       </c>
@@ -1404,15 +3407,8 @@
       <c r="S26" s="10">
         <v>2.1429999999999998</v>
       </c>
-      <c r="T26">
-        <v>1.6</v>
-      </c>
-      <c r="U26">
-        <f t="shared" si="0"/>
-        <v>2.4095</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21">
+    </row>
+    <row r="27" spans="1:26" ht="14">
       <c r="B27" s="7" t="s">
         <v>27</v>
       </c>
@@ -1462,14 +3458,30 @@
         <v>2.16</v>
       </c>
       <c r="T27">
-        <v>1.4</v>
+        <v>0.13999999999999999</v>
       </c>
       <c r="U27">
         <f t="shared" si="0"/>
         <v>2.415</v>
       </c>
-    </row>
-    <row r="28" spans="1:21">
+      <c r="V27">
+        <f t="shared" ref="V27:V39" si="1">U27-0.076</f>
+        <v>2.339</v>
+      </c>
+      <c r="W27">
+        <v>2.3479999999999999</v>
+      </c>
+      <c r="X27">
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="Y27">
+        <v>2.4239999999999999</v>
+      </c>
+      <c r="Z27">
+        <v>2.3479999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26" ht="14">
       <c r="B28" s="7" t="s">
         <v>28</v>
       </c>
@@ -1519,14 +3531,30 @@
         <v>1.847</v>
       </c>
       <c r="T28">
-        <v>1.2</v>
+        <v>0.12</v>
       </c>
       <c r="U28">
         <f t="shared" si="0"/>
         <v>2.0220000000000002</v>
       </c>
-    </row>
-    <row r="29" spans="1:21">
+      <c r="V28">
+        <f t="shared" si="1"/>
+        <v>1.9460000000000002</v>
+      </c>
+      <c r="W28">
+        <v>2.0249999999999999</v>
+      </c>
+      <c r="X28">
+        <v>0.12</v>
+      </c>
+      <c r="Y28">
+        <v>2.101</v>
+      </c>
+      <c r="Z28">
+        <v>2.0249999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:26" ht="14">
       <c r="B29" s="7" t="s">
         <v>29</v>
       </c>
@@ -1576,14 +3604,30 @@
         <v>1.716</v>
       </c>
       <c r="T29">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U29">
         <f t="shared" si="0"/>
         <v>1.6400000000000001</v>
       </c>
-    </row>
-    <row r="30" spans="1:21">
+      <c r="V29">
+        <f t="shared" si="1"/>
+        <v>1.5640000000000001</v>
+      </c>
+      <c r="W29">
+        <v>1.637</v>
+      </c>
+      <c r="X29">
+        <v>0.1</v>
+      </c>
+      <c r="Y29">
+        <v>1.7130000000000001</v>
+      </c>
+      <c r="Z29">
+        <v>1.637</v>
+      </c>
+    </row>
+    <row r="30" spans="1:26" ht="14">
       <c r="B30" s="7" t="s">
         <v>30</v>
       </c>
@@ -1633,14 +3677,30 @@
         <v>1.31</v>
       </c>
       <c r="T30">
-        <v>0.8</v>
+        <v>8.0000000000000016E-2</v>
       </c>
       <c r="U30">
         <f t="shared" si="0"/>
         <v>1.3130000000000002</v>
       </c>
-    </row>
-    <row r="31" spans="1:21">
+      <c r="V30">
+        <f t="shared" si="1"/>
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="W30">
+        <v>1.3499999999999999</v>
+      </c>
+      <c r="X30">
+        <v>8.0000000000000016E-2</v>
+      </c>
+      <c r="Y30">
+        <v>1.4259999999999999</v>
+      </c>
+      <c r="Z30">
+        <v>1.3499999999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:26" ht="14">
       <c r="B31" s="7" t="s">
         <v>31</v>
       </c>
@@ -1690,14 +3750,30 @@
         <v>0.85899999999999999</v>
       </c>
       <c r="T31">
-        <v>0.6</v>
+        <v>0.06</v>
       </c>
       <c r="U31">
         <f t="shared" si="0"/>
         <v>0.86349999999999993</v>
       </c>
-    </row>
-    <row r="32" spans="1:21">
+      <c r="V31">
+        <f t="shared" si="1"/>
+        <v>0.78749999999999998</v>
+      </c>
+      <c r="W31">
+        <v>0.88500000000000001</v>
+      </c>
+      <c r="X31">
+        <v>0.06</v>
+      </c>
+      <c r="Y31">
+        <v>0.96099999999999997</v>
+      </c>
+      <c r="Z31">
+        <v>0.88500000000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:26" ht="14">
       <c r="B32" s="7" t="s">
         <v>32</v>
       </c>
@@ -1747,14 +3823,30 @@
         <v>0.77100000000000002</v>
       </c>
       <c r="T32">
-        <v>0.4</v>
+        <v>4.0000000000000008E-2</v>
       </c>
       <c r="U32">
         <f t="shared" si="0"/>
         <v>0.77249999999999996</v>
       </c>
-    </row>
-    <row r="33" spans="18:21">
+      <c r="V32">
+        <f t="shared" si="1"/>
+        <v>0.69650000000000001</v>
+      </c>
+      <c r="W32">
+        <v>0.749</v>
+      </c>
+      <c r="X32">
+        <v>4.0000000000000008E-2</v>
+      </c>
+      <c r="Y32">
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="Z32">
+        <v>0.749</v>
+      </c>
+    </row>
+    <row r="33" spans="3:28">
       <c r="R33" s="14">
         <v>0.34799999999999998</v>
       </c>
@@ -1762,14 +3854,30 @@
         <v>0.35899999999999999</v>
       </c>
       <c r="T33">
-        <v>0.2</v>
+        <v>2.0000000000000004E-2</v>
       </c>
       <c r="U33">
         <f t="shared" si="0"/>
         <v>0.35349999999999998</v>
       </c>
-    </row>
-    <row r="34" spans="18:21">
+      <c r="V33">
+        <f t="shared" si="1"/>
+        <v>0.27749999999999997</v>
+      </c>
+      <c r="W33">
+        <v>0.315</v>
+      </c>
+      <c r="X33">
+        <v>2.0000000000000004E-2</v>
+      </c>
+      <c r="Y33">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="Z33">
+        <v>0.315</v>
+      </c>
+    </row>
+    <row r="34" spans="3:28">
       <c r="R34" s="12">
         <v>0.222</v>
       </c>
@@ -1777,14 +3885,30 @@
         <v>0.25600000000000001</v>
       </c>
       <c r="T34">
-        <v>0.1</v>
+        <v>1.0000000000000002E-2</v>
       </c>
       <c r="U34">
         <f t="shared" si="0"/>
         <v>0.23899999999999999</v>
       </c>
-    </row>
-    <row r="35" spans="18:21">
+      <c r="V34">
+        <f t="shared" si="1"/>
+        <v>0.16299999999999998</v>
+      </c>
+      <c r="W34">
+        <v>0.18049999999999999</v>
+      </c>
+      <c r="X34">
+        <v>1.0000000000000002E-2</v>
+      </c>
+      <c r="Y34">
+        <v>0.25650000000000001</v>
+      </c>
+      <c r="Z34">
+        <v>0.18049999999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="3:28">
       <c r="R35" s="12">
         <v>0.17699999999999999</v>
       </c>
@@ -1792,14 +3916,30 @@
         <v>0.182</v>
       </c>
       <c r="T35">
-        <v>0.08</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="U35">
         <f t="shared" si="0"/>
         <v>0.17949999999999999</v>
       </c>
-    </row>
-    <row r="36" spans="18:21">
+      <c r="V35">
+        <f t="shared" si="1"/>
+        <v>0.10349999999999999</v>
+      </c>
+      <c r="W35">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="X35">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="Y35">
+        <v>0.192</v>
+      </c>
+      <c r="Z35">
+        <v>0.11600000000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="3:28">
       <c r="R36" s="12">
         <v>0.14199999999999999</v>
       </c>
@@ -1807,14 +3947,30 @@
         <v>0.14599999999999999</v>
       </c>
       <c r="T36">
-        <v>0.04</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="U36">
         <f t="shared" si="0"/>
         <v>0.14399999999999999</v>
       </c>
-    </row>
-    <row r="37" spans="18:21">
+      <c r="V36">
+        <f t="shared" si="1"/>
+        <v>6.7999999999999991E-2</v>
+      </c>
+      <c r="W36">
+        <v>7.2499999999999995E-2</v>
+      </c>
+      <c r="X36">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="Y36">
+        <v>0.14849999999999999</v>
+      </c>
+      <c r="Z36">
+        <v>7.2499999999999995E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="3:28">
       <c r="R37" s="12">
         <v>0.14399999999999999</v>
       </c>
@@ -1822,14 +3978,30 @@
         <v>9.6000000000000002E-2</v>
       </c>
       <c r="T37">
-        <v>0.02</v>
+        <v>2E-3</v>
       </c>
       <c r="U37">
         <f t="shared" si="0"/>
         <v>0.12</v>
       </c>
-    </row>
-    <row r="38" spans="18:21">
+      <c r="V37">
+        <f t="shared" si="1"/>
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="W37">
+        <v>4.7E-2</v>
+      </c>
+      <c r="X37">
+        <v>2E-3</v>
+      </c>
+      <c r="Y37">
+        <v>0.123</v>
+      </c>
+      <c r="Z37">
+        <v>4.7E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="3:28">
       <c r="R38" s="12">
         <v>8.3000000000000004E-2</v>
       </c>
@@ -1837,14 +4009,55 @@
         <v>8.1000000000000003E-2</v>
       </c>
       <c r="T38">
-        <v>0.01</v>
+        <v>1E-3</v>
       </c>
       <c r="U38">
         <f t="shared" si="0"/>
         <v>8.2000000000000003E-2</v>
       </c>
-    </row>
-    <row r="39" spans="18:21">
+      <c r="V38">
+        <f t="shared" si="1"/>
+        <v>6.0000000000000053E-3</v>
+      </c>
+      <c r="W38">
+        <v>6.5000000000000058E-3</v>
+      </c>
+      <c r="X38">
+        <v>1E-3</v>
+      </c>
+      <c r="Y38">
+        <v>8.2500000000000004E-2</v>
+      </c>
+      <c r="Z38">
+        <v>6.5000000000000058E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="3:28">
+      <c r="C39" cm="1">
+        <f t="array" ref="C39:J44">TRANSPOSE(C25:H32)</f>
+        <v>0.77400000000000002</v>
+      </c>
+      <c r="D39">
+        <v>0.34799999999999998</v>
+      </c>
+      <c r="E39">
+        <v>0.222</v>
+      </c>
+      <c r="F39">
+        <v>0.17699999999999999</v>
+      </c>
+      <c r="G39">
+        <v>0.14199999999999999</v>
+      </c>
+      <c r="H39">
+        <v>0.14399999999999999</v>
+      </c>
+      <c r="I39">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="J39">
+        <v>8.2000000000000003E-2</v>
+      </c>
       <c r="R39" s="12">
         <v>8.2000000000000003E-2</v>
       </c>
@@ -1858,8 +4071,451 @@
         <f t="shared" si="0"/>
         <v>7.6000000000000012E-2</v>
       </c>
+      <c r="V39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0</v>
+      </c>
+      <c r="X39">
+        <v>0</v>
+      </c>
+      <c r="Y39">
+        <v>7.6000000000000012E-2</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="3:28">
+      <c r="C40">
+        <v>0.77100000000000002</v>
+      </c>
+      <c r="D40">
+        <v>0.35899999999999999</v>
+      </c>
+      <c r="E40">
+        <v>0.25600000000000001</v>
+      </c>
+      <c r="F40">
+        <v>0.182</v>
+      </c>
+      <c r="G40">
+        <v>0.14599999999999999</v>
+      </c>
+      <c r="H40">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="I40">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="J40">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="3:28">
+      <c r="C41">
+        <v>2.4020000000000001</v>
+      </c>
+      <c r="D41">
+        <v>3.08</v>
+      </c>
+      <c r="E41">
+        <v>2.6760000000000002</v>
+      </c>
+      <c r="F41">
+        <v>2.67</v>
+      </c>
+      <c r="G41">
+        <v>2.1970000000000001</v>
+      </c>
+      <c r="H41">
+        <v>1.5640000000000001</v>
+      </c>
+      <c r="I41">
+        <v>1.3160000000000001</v>
+      </c>
+      <c r="J41">
+        <v>0.86799999999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="3:28">
+      <c r="C42">
+        <v>2.1309999999999998</v>
+      </c>
+      <c r="D42">
+        <v>2.504</v>
+      </c>
+      <c r="E42">
+        <v>2.1429999999999998</v>
+      </c>
+      <c r="F42">
+        <v>2.16</v>
+      </c>
+      <c r="G42">
+        <v>1.847</v>
+      </c>
+      <c r="H42">
+        <v>1.716</v>
+      </c>
+      <c r="I42">
+        <v>1.31</v>
+      </c>
+      <c r="J42">
+        <v>0.85899999999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="3:28">
+      <c r="C43">
+        <v>3.2330000000000001</v>
+      </c>
+      <c r="D43">
+        <v>3.2610000000000001</v>
+      </c>
+      <c r="E43">
+        <v>3.3730000000000002</v>
+      </c>
+      <c r="F43">
+        <v>3.3220000000000001</v>
+      </c>
+      <c r="G43">
+        <v>2.9460000000000002</v>
+      </c>
+      <c r="H43">
+        <v>2.798</v>
+      </c>
+      <c r="I43">
+        <v>2.403</v>
+      </c>
+      <c r="J43">
+        <v>3.0880000000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="3:28">
+      <c r="C44">
+        <v>3.2170000000000001</v>
+      </c>
+      <c r="D44">
+        <v>3.141</v>
+      </c>
+      <c r="E44">
+        <v>3.1890000000000001</v>
+      </c>
+      <c r="F44">
+        <v>3.3820000000000001</v>
+      </c>
+      <c r="G44">
+        <v>3.3140000000000001</v>
+      </c>
+      <c r="H44">
+        <v>3.4020000000000001</v>
+      </c>
+      <c r="I44">
+        <v>3.169</v>
+      </c>
+      <c r="J44">
+        <v>2.1219999999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="3:28">
+      <c r="L45">
+        <v>8</v>
+      </c>
+      <c r="M45">
+        <v>7</v>
+      </c>
+      <c r="N45">
+        <v>6</v>
+      </c>
+      <c r="O45">
+        <v>5</v>
+      </c>
+      <c r="P45">
+        <v>4</v>
+      </c>
+      <c r="Q45">
+        <v>3</v>
+      </c>
+      <c r="R45">
+        <v>2</v>
+      </c>
+      <c r="S45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="3:28">
+      <c r="L46">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="M46">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="N46">
+        <v>0.14399999999999999</v>
+      </c>
+      <c r="O46">
+        <v>0.14199999999999999</v>
+      </c>
+      <c r="P46">
+        <v>0.17699999999999999</v>
+      </c>
+      <c r="Q46">
+        <v>0.222</v>
+      </c>
+      <c r="R46">
+        <v>0.34799999999999998</v>
+      </c>
+      <c r="S46">
+        <v>0.77400000000000002</v>
+      </c>
+      <c r="U46">
+        <v>3.0880000000000001</v>
+      </c>
+      <c r="V46">
+        <v>2.403</v>
+      </c>
+      <c r="W46">
+        <v>2.798</v>
+      </c>
+      <c r="X46">
+        <v>2.9460000000000002</v>
+      </c>
+      <c r="Y46">
+        <v>3.3220000000000001</v>
+      </c>
+      <c r="Z46">
+        <v>3.3730000000000002</v>
+      </c>
+      <c r="AA46">
+        <v>3.2610000000000001</v>
+      </c>
+      <c r="AB46">
+        <v>3.2330000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="3:28">
+      <c r="L47">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M47">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="N47">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="O47">
+        <v>0.14599999999999999</v>
+      </c>
+      <c r="P47">
+        <v>0.182</v>
+      </c>
+      <c r="Q47">
+        <v>0.25600000000000001</v>
+      </c>
+      <c r="R47">
+        <v>0.35899999999999999</v>
+      </c>
+      <c r="S47">
+        <v>0.77100000000000002</v>
+      </c>
+      <c r="U47">
+        <v>2.1219999999999999</v>
+      </c>
+      <c r="V47">
+        <v>3.169</v>
+      </c>
+      <c r="W47">
+        <v>3.4020000000000001</v>
+      </c>
+      <c r="X47">
+        <v>3.3140000000000001</v>
+      </c>
+      <c r="Y47">
+        <v>3.3820000000000001</v>
+      </c>
+      <c r="Z47">
+        <v>3.1890000000000001</v>
+      </c>
+      <c r="AA47">
+        <v>3.141</v>
+      </c>
+      <c r="AB47">
+        <v>3.2170000000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="3:28">
+      <c r="L48">
+        <v>0.86799999999999999</v>
+      </c>
+      <c r="M48">
+        <v>1.3160000000000001</v>
+      </c>
+      <c r="N48">
+        <v>1.5640000000000001</v>
+      </c>
+      <c r="O48">
+        <v>2.1970000000000001</v>
+      </c>
+      <c r="P48">
+        <v>2.67</v>
+      </c>
+      <c r="Q48">
+        <v>2.6760000000000002</v>
+      </c>
+      <c r="R48">
+        <v>3.08</v>
+      </c>
+      <c r="S48">
+        <v>2.4020000000000001</v>
+      </c>
+      <c r="U48">
+        <f>(U46+U47)/2</f>
+        <v>2.605</v>
+      </c>
+      <c r="V48">
+        <f>(V46+V47)/2</f>
+        <v>2.786</v>
+      </c>
+      <c r="W48">
+        <f>(W46+W47)/2</f>
+        <v>3.1</v>
+      </c>
+      <c r="X48">
+        <f>(X46+X47)/2</f>
+        <v>3.13</v>
+      </c>
+      <c r="Y48">
+        <f>(Y46+Y47)/2</f>
+        <v>3.3520000000000003</v>
+      </c>
+      <c r="Z48">
+        <f>(Z46+Z47)/2</f>
+        <v>3.2810000000000001</v>
+      </c>
+      <c r="AA48">
+        <f>(AA46+AA47)/2</f>
+        <v>3.2010000000000001</v>
+      </c>
+      <c r="AB48">
+        <f>(AB46+AB47)/2</f>
+        <v>3.2250000000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="12:28">
+      <c r="L49">
+        <v>0.85899999999999999</v>
+      </c>
+      <c r="M49">
+        <v>1.31</v>
+      </c>
+      <c r="N49">
+        <v>1.716</v>
+      </c>
+      <c r="O49">
+        <v>1.847</v>
+      </c>
+      <c r="P49">
+        <v>2.16</v>
+      </c>
+      <c r="Q49">
+        <v>2.1429999999999998</v>
+      </c>
+      <c r="R49">
+        <v>2.504</v>
+      </c>
+      <c r="S49">
+        <v>2.1309999999999998</v>
+      </c>
+      <c r="U49">
+        <f>ABS(U46-U47)</f>
+        <v>0.96600000000000019</v>
+      </c>
+      <c r="V49">
+        <f t="shared" ref="V49:AB49" si="2">ABS(V46-V47)</f>
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="W49">
+        <f t="shared" si="2"/>
+        <v>0.60400000000000009</v>
+      </c>
+      <c r="X49">
+        <f t="shared" si="2"/>
+        <v>0.36799999999999988</v>
+      </c>
+      <c r="Y49">
+        <f t="shared" si="2"/>
+        <v>6.0000000000000053E-2</v>
+      </c>
+      <c r="Z49">
+        <f t="shared" si="2"/>
+        <v>0.18400000000000016</v>
+      </c>
+      <c r="AA49">
+        <f t="shared" si="2"/>
+        <v>0.12000000000000011</v>
+      </c>
+      <c r="AB49">
+        <f t="shared" si="2"/>
+        <v>1.6000000000000014E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="12:28">
+      <c r="L50">
+        <v>3.0880000000000001</v>
+      </c>
+      <c r="M50">
+        <v>2.403</v>
+      </c>
+      <c r="N50">
+        <v>2.798</v>
+      </c>
+      <c r="O50">
+        <v>2.9460000000000002</v>
+      </c>
+      <c r="P50">
+        <v>3.3220000000000001</v>
+      </c>
+      <c r="Q50">
+        <v>3.3730000000000002</v>
+      </c>
+      <c r="R50">
+        <v>3.2610000000000001</v>
+      </c>
+      <c r="S50">
+        <v>3.2330000000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="12:28">
+      <c r="L51">
+        <v>2.1219999999999999</v>
+      </c>
+      <c r="M51">
+        <v>3.169</v>
+      </c>
+      <c r="N51">
+        <v>3.4020000000000001</v>
+      </c>
+      <c r="O51">
+        <v>3.3140000000000001</v>
+      </c>
+      <c r="P51">
+        <v>3.3820000000000001</v>
+      </c>
+      <c r="Q51">
+        <v>3.1890000000000001</v>
+      </c>
+      <c r="R51">
+        <v>3.141</v>
+      </c>
+      <c r="S51">
+        <v>3.2170000000000001</v>
+      </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" columnSort="1" ref="L45:S51">
+    <sortCondition descending="1" ref="L45:S45"/>
+  </sortState>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="256" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
